--- a/02 - Stakeholderanalyse/StakeholderAnalyse.xlsx
+++ b/02 - Stakeholderanalyse/StakeholderAnalyse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7b5b5fcebf85018c/Documents/personal Documents/01 - Studien/06 -MSc/1. Semester/SED605 - Requirements Engineering/Abgabe 2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\Study-Buddy-Gruppe06\02 - Stakeholderanalyse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07BA3A31-D361-43DA-A167-1ADA79EF485F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ABBC09-6452-444F-8995-24015B8A94CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{09E038EE-F597-412F-87BA-8876B6EC60A2}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="38700" windowHeight="15345" xr2:uid="{09E038EE-F597-412F-87BA-8876B6EC60A2}"/>
   </bookViews>
   <sheets>
     <sheet name="Stakeholder Analyse" sheetId="10" r:id="rId1"/>
@@ -219,19 +219,6 @@
 </t>
   </si>
   <si>
-    <t>Interessen: 
-Die Studierenden sollen unterstützt werden, ohne dabei überwacht zu werden. Durch die verschiedenen Herangehensweisen (Uhrzeiten, Timings, Settings, etc.) kann anhand von Login's nicht nachvollzogen werden, ob die oder der Studierende Schwierigkeiten im Lernfortschritt hat. Durch die große Benachrichtigungsflut ist der Mehrwert einer weiteren Benachrichtigung überschaubar und müsste parametrisierbar sein um funktionell zu sein. Die sehr frühe Einbindung der Studierendenvertretung ist wünschenswert. 
-Werte:
-Autonomie und Selbstbestimmung, individuelle Lebenssituationen, Partizipation, Transparenz, Freiwilligkeit der Nutzung
-Konflikte:
--&gt; Studiengangsleitung: Wer bestimmt welche Inaktivität und welche verpasste Abgabe als Warnsignal angesehen werden muss ? Hier steht der Wunsch nach formellen Rahmenbedingungen im Konflikt mit einer individuellen Lerngeschwindigkeit und dem Wunsch nach Selbstbestimmung.
--&gt; Datenlogik: Technische Messbarkeit legt sich beispielsweise auf Daten wie Login-Zeiträume. Nehmen sich Studierende jedoch nur einmal pro Woche ganze Tage Zeit, stehen diese automatisch am Frühwarnsystem, obwohl sie ihr Studium dahingehend organisiert haben. 
--&gt; Benachrichtigungen: Durch die Benachrichtigungsflut die Studierende tagtäglich haben, würde ein Warnsystem eventuell nur diese Flut vergrößern und somit den Merhwert ad absurdum führen.
--&gt;Partizipation am Projekt: Wird den Studierenden ein fertiges System vorgelegt,  kann das System eher als Kontrollsystem statt Unterstützungssystem angesehen werden. Die Akzeptanz und das Vertrauen wären damit gering. 
-Beeinflussungsgrad
-Betroffenheitsgrad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Interessen:
 Die Lehrendenvertretung hält es grundsätzlich für sinnvoll, Studierende bei der Organisation ihres Lernens zu unterstützen. Der Study Buddy muss aber berücksichtigen, dass Lehrveranstaltungen sehr unterschiedlich aufgebaut sind: wöchentliche Aufgaben, längere Selbstlernphasen, freiwillige und verpflichtende Aktivitäten. Es muss geklärt werden, woran das System erkennt, welche Aktivitäten überhaupt relevant sind. Ebenso offen ist die Rolle der Lehrenden: Müssen sie zusätzliche Informationen pflegen, und werden sie automatisch benachrichtigt? Zusätzlicher administrativer Aufwand soll vermieden werden. Studierende sollen nicht aufgrund unvollständiger Daten falsch eingeschätzt werden. Die Lehrendenvertretung bietet an, ihre Erfahrungen einzubringen.
 Werte:
@@ -245,6 +232,17 @@
   </si>
   <si>
     <t xml:space="preserve">Wie in Mission 1 beschreiben. Detaillierte Stakeholderanalyse liegt bereits vor. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interessen: 
+Die Studierenden sollen unterstützt werden, ohne dabei überwacht zu werden. Durch die verschiedenen Herangehensweisen (Uhrzeiten, Timings, Settings, etc.) kann anhand von Login's nicht nachvollzogen werden, ob die oder der Studierende Schwierigkeiten im Lernfortschritt hat. Durch die große Benachrichtigungsflut ist der Mehrwert einer weiteren Benachrichtigung überschaubar und müsste parametrisierbar sein um funktionell zu sein. Die sehr frühe Einbindung der Studierendenvertretung ist wünschenswert. 
+Werte:
+Autonomie und Selbstbestimmung, individuelle Lebenssituationen, Partizipation, Transparenz, Freiwilligkeit der Nutzung
+Konflikte:
+-&gt; Studiengangsleitung: Wer bestimmt welche Inaktivität und welche verpasste Abgabe als Warnsignal angesehen werden muss ? Hier steht der Wunsch nach formellen Rahmenbedingungen im Konflikt mit einer individuellen Lerngeschwindigkeit und dem Wunsch nach Selbstbestimmung.
+-&gt; Datenlogik: Technische Messbarkeit legt sich beispielsweise auf Daten wie Login-Zeiträume. Nehmen sich Studierende jedoch nur einmal pro Woche ganze Tage Zeit, stehen diese automatisch am Frühwarnsystem, obwohl sie ihr Studium dahingehend organisiert haben. 
+-&gt; Benachrichtigungen: Durch die Benachrichtigungsflut die Studierende tagtäglich haben, würde ein Warnsystem eventuell nur diese Flut vergrößern und somit den Merhwert ad absurdum führen.
+-&gt;Partizipation am Projekt: Wird den Studierenden ein fertiges System vorgelegt,  kann das System eher als Kontrollsystem statt Unterstützungssystem angesehen werden. Die Akzeptanz und das Vertrauen wären damit gering. </t>
   </si>
 </sst>
 </file>
@@ -470,11 +468,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -699,7 +697,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E6B752BC-81DC-4C96-BA5A-0707D841CBD9}" type="CELLRANGE">
+                    <a:fld id="{A373D3F8-DD93-4808-9723-6C5273090C8A}" type="CELLRANGE">
                       <a:rPr lang="en-GB"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1916,42 +1914,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="15"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:7" ht="13.5" thickBot="1"/>
     <row r="6" spans="1:7" ht="39" thickBot="1">
@@ -1974,12 +1972,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="344.25">
+    <row r="7" spans="1:7" ht="293.25">
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>20</v>
+      <c r="C7" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="9">
         <v>9</v>
@@ -2000,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="9">
         <v>10</v>
@@ -2042,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3">
         <v>9</v>
@@ -2063,7 +2061,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3">
         <v>10</v>
@@ -2323,18 +2321,18 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2356,18 +2354,18 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE14945-2D7D-4C82-B3E0-1E2097BFA55F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE408F5E-A533-43F5-B6C0-764D24E207E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE408F5E-A533-43F5-B6C0-764D24E207E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE14945-2D7D-4C82-B3E0-1E2097BFA55F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
